--- a/Team-Data/2008-09/3-18-2008-09.xlsx
+++ b/Team-Data/2008-09/3-18-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -781,7 +848,7 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -799,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -858,52 +925,52 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
         <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
@@ -912,16 +979,16 @@
         <v>23.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,10 +1018,10 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
         <v>6</v>
@@ -966,7 +1033,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -978,22 +1045,22 @@
         <v>29</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1025,85 +1092,85 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.441</v>
+        <v>0.433</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1127,13 +1194,13 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1145,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
@@ -1154,13 +1221,13 @@
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1169,16 +1236,16 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1222,43 +1289,43 @@
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
         <v>14.9</v>
@@ -1270,22 +1337,22 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1309,58 +1376,58 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM5" t="n">
         <v>23</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
         <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="H6" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.754</v>
@@ -1434,40 +1501,40 @@
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.7</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,10 +1567,10 @@
         <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
@@ -1512,31 +1579,31 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1691,19 +1758,19 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.638</v>
+        <v>0.632</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,7 +1838,7 @@
         <v>36.8</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.466</v>
@@ -1780,10 +1847,10 @@
         <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
@@ -1792,7 +1859,7 @@
         <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
         <v>11.2</v>
@@ -1804,10 +1871,10 @@
         <v>41.7</v>
       </c>
       <c r="U8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W8" t="n">
         <v>8.5</v>
@@ -1816,7 +1883,7 @@
         <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z8" t="n">
         <v>22.8</v>
@@ -1825,22 +1892,22 @@
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.2</v>
+        <v>103</v>
       </c>
       <c r="AC8" t="n">
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="n">
         <v>7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -1894,7 +1961,7 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J9" t="n">
-        <v>80.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,31 +2032,31 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R9" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T9" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>6.3</v>
@@ -1998,7 +2065,7 @@
         <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="n">
         <v>21.1</v>
@@ -2007,13 +2074,13 @@
         <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2025,13 +2092,13 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2055,13 +2122,13 @@
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2076,7 +2143,7 @@
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2243,10 +2310,10 @@
         <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.643</v>
+        <v>0.638</v>
       </c>
       <c r="H11" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K11" t="n">
         <v>0.451</v>
@@ -2326,7 +2393,7 @@
         <v>7.6</v>
       </c>
       <c r="M11" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="N11" t="n">
         <v>0.371</v>
@@ -2338,28 +2405,28 @@
         <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.805</v>
+        <v>0.806</v>
       </c>
       <c r="R11" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S11" t="n">
         <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V11" t="n">
         <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
@@ -2371,7 +2438,7 @@
         <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>3.8</v>
@@ -2380,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
@@ -2419,16 +2486,16 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2437,7 +2504,7 @@
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>22</v>
@@ -2452,7 +2519,7 @@
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -2481,88 +2548,88 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
         <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L12" t="n">
         <v>7.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O12" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P12" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
         <v>43.5</v>
       </c>
       <c r="U12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>104</v>
+        <v>104.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2592,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
         <v>23</v>
@@ -2601,7 +2668,7 @@
         <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -2663,43 +2730,43 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
         <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>0.25</v>
+        <v>0.239</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J13" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>17.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
         <v>0.744</v>
@@ -2714,37 +2781,37 @@
         <v>40.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="n">
         <v>5.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA13" t="n">
         <v>19.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.7</v>
+        <v>95.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2771,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2786,13 +2853,13 @@
         <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2807,10 +2874,10 @@
         <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -2845,55 +2912,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.788</v>
+        <v>0.791</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
@@ -2905,7 +2972,7 @@
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
@@ -2914,16 +2981,16 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.2</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2938,7 +3005,7 @@
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,10 +3053,10 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.254</v>
+        <v>0.258</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J15" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
       <c r="K15" t="n">
         <v>0.45</v>
@@ -3057,7 +3124,7 @@
         <v>13.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O15" t="n">
         <v>18.9</v>
@@ -3066,46 +3133,46 @@
         <v>25.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S15" t="n">
         <v>28.4</v>
       </c>
       <c r="T15" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
         <v>17.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
         <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.5</v>
+        <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>24</v>
@@ -3165,13 +3232,13 @@
         <v>11</v>
       </c>
       <c r="AX15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>20</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="n">
         <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>0.537</v>
+        <v>0.545</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -3239,16 +3306,16 @@
         <v>19.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O16" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P16" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
@@ -3260,13 +3327,13 @@
         <v>39.3</v>
       </c>
       <c r="U16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V16" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>5.6</v>
@@ -3275,31 +3342,31 @@
         <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
         <v>10</v>
@@ -3323,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3338,7 +3405,7 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3353,10 +3420,10 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3406,49 +3473,49 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3460,16 +3527,16 @@
         <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3481,10 +3548,10 @@
         <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3493,7 +3560,7 @@
         <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>20</v>
@@ -3502,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
         <v>9</v>
@@ -3511,13 +3578,13 @@
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3573,49 +3640,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.294</v>
+        <v>0.299</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
         <v>0.442</v>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N18" t="n">
         <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P18" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0.773</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S18" t="n">
         <v>29.9</v>
@@ -3630,7 +3697,7 @@
         <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X18" t="n">
         <v>4.1</v>
@@ -3642,16 +3709,16 @@
         <v>22.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
         <v>-4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3678,16 +3745,16 @@
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN18" t="n">
         <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -3699,19 +3766,19 @@
         <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.426</v>
+        <v>0.418</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.45</v>
+        <v>0.447</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
@@ -3785,19 +3852,19 @@
         <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="P19" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0.783</v>
       </c>
       <c r="R19" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S19" t="n">
         <v>29.3</v>
@@ -3806,7 +3873,7 @@
         <v>39.7</v>
       </c>
       <c r="U19" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V19" t="n">
         <v>13.2</v>
@@ -3821,28 +3888,28 @@
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.2</v>
+        <v>-2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>10</v>
@@ -3854,7 +3921,7 @@
         <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>4</v>
@@ -3866,19 +3933,19 @@
         <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT19" t="n">
         <v>24</v>
@@ -3893,22 +3960,22 @@
         <v>21</v>
       </c>
       <c r="AX19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY19" t="n">
         <v>16</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3964,10 +4031,10 @@
         <v>7.2</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O20" t="n">
         <v>18.4</v>
@@ -3991,7 +4058,7 @@
         <v>19.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
         <v>7.3</v>
@@ -4000,28 +4067,28 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA20" t="n">
         <v>20.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
         <v>9</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4045,19 +4112,19 @@
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
@@ -4066,13 +4133,13 @@
         <v>23</v>
       </c>
       <c r="AU20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4081,10 +4148,10 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
         <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4143,22 +4210,22 @@
         <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="R21" t="n">
         <v>11.1</v>
@@ -4170,7 +4237,7 @@
         <v>42.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
         <v>14.4</v>
@@ -4182,34 +4249,34 @@
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA21" t="n">
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.8</v>
+        <v>106.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="n">
         <v>20</v>
       </c>
-      <c r="AE21" t="n">
-        <v>21</v>
-      </c>
       <c r="AF21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG21" t="n">
         <v>20</v>
       </c>
-      <c r="AG21" t="n">
-        <v>21</v>
-      </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4236,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4254,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" t="n">
         <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.279</v>
+        <v>0.284</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4331,13 +4398,13 @@
         <v>11.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O22" t="n">
         <v>20.2</v>
       </c>
       <c r="P22" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q22" t="n">
         <v>0.787</v>
@@ -4346,40 +4413,40 @@
         <v>12.4</v>
       </c>
       <c r="S22" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.5</v>
+        <v>-5.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,16 +4458,16 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,10 +4476,10 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -4424,19 +4491,19 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT22" t="n">
         <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,10 +4512,10 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,10 +4568,10 @@
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>10.3</v>
@@ -4513,28 +4580,28 @@
         <v>26.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O23" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P23" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
         <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V23" t="n">
         <v>14.3</v>
@@ -4543,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="X23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y23" t="n">
         <v>3.7</v>
@@ -4558,28 +4625,28 @@
         <v>102.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>10</v>
@@ -4594,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4618,16 +4685,16 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
         <v>34</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
         <v>80.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M24" t="n">
         <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.314</v>
       </c>
       <c r="O24" t="n">
         <v>19.1</v>
       </c>
       <c r="P24" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R24" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S24" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T24" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U24" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -4728,7 +4795,7 @@
         <v>5.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
         <v>20</v>
@@ -4737,19 +4804,19 @@
         <v>21.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -4758,13 +4825,13 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ24" t="n">
         <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
         <v>8</v>
@@ -4788,10 +4855,10 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
         <v>18</v>
@@ -4806,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -4847,49 +4914,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.544</v>
+        <v>0.537</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="J25" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P25" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
         <v>0.755</v>
       </c>
       <c r="R25" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S25" t="n">
         <v>30.9</v>
@@ -4898,10 +4965,10 @@
         <v>41.2</v>
       </c>
       <c r="U25" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V25" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W25" t="n">
         <v>7</v>
@@ -4913,37 +4980,37 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA25" t="n">
         <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>108.5</v>
+        <v>108.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4973,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
@@ -4982,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5032,43 +5099,43 @@
         <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>0.642</v>
+        <v>0.627</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
         <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
         <v>24.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5092,22 +5159,22 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5116,13 +5183,13 @@
         <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI26" t="n">
         <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5131,7 +5198,7 @@
         <v>8</v>
       </c>
       <c r="AL26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM26" t="n">
         <v>13</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="n">
         <v>17</v>
       </c>
-      <c r="AP26" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,10 +5222,10 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,10 +5296,10 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
@@ -5241,13 +5308,13 @@
         <v>19</v>
       </c>
       <c r="N27" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.803</v>
@@ -5256,40 +5323,40 @@
         <v>10</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="T27" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="U27" t="n">
         <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z27" t="n">
         <v>23.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5310,7 +5377,7 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>12</v>
@@ -5319,34 +5386,34 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5665,13 +5732,13 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
         <v>18</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>15</v>
@@ -5689,7 +5756,7 @@
         <v>18</v>
       </c>
       <c r="AP29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5713,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -5853,7 +5920,7 @@
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5883,7 +5950,7 @@
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>0.232</v>
+        <v>0.235</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P31" t="n">
         <v>23</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R31" t="n">
         <v>11.6</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="T31" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>4.2</v>
@@ -6008,19 +6075,19 @@
         <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
         <v>29</v>
@@ -6029,16 +6096,16 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6056,7 +6123,7 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6068,13 +6135,13 @@
         <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-18-2008-09</t>
+          <t>2009-03-18</t>
         </is>
       </c>
     </row>
